--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,6 +892,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128856466</v>
+      </c>
+      <c r="B4" t="n">
+        <v>86814</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>439</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sydlig gyllenspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius bergeronii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Melot) Melot</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörkavad, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442259</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6186188</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degeberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkrik bokskog</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86814</v>
+        <v>86818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86818</v>
+        <v>86822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86822</v>
+        <v>86827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86834</v>
+        <v>86837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke</t>
+          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86837</v>
+        <v>86840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
+          <t>Gunilla R Burke, Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Jan  Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Jan  Olsson</t>
+          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
+          <t>Jan  Olsson, Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86840</v>
+        <v>86844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan  Olsson, Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Joachim Krumlinde, Maria Ahlefelt, Ulf Arup, Gabriella Fjordmark Lerne, Clara Lerbro, Vincent Vitlock, Annika Norin, Jan  Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86844</v>
+        <v>86851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Joachim Krumlinde, Maria Ahlefelt, Ulf Arup, Gabriella Fjordmark Lerne, Clara Lerbro, Vincent Vitlock, Annika Norin, Jan  Olsson</t>
+          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86851</v>
+        <v>86853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86853</v>
+        <v>86854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128856466</v>
       </c>
       <c r="B4" t="n">
-        <v>86854</v>
+        <v>86857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119032492</v>
+        <v>128856466</v>
       </c>
       <c r="B2" t="n">
-        <v>56261</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Sydlig gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Cortinarius bergeronii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Melot) Melot</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>längsbäcken, Sk</t>
+          <t>Mörkavad, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442221</v>
+        <v>442259</v>
       </c>
       <c r="R2" t="n">
-        <v>6186208</v>
+        <v>6186188</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,34 +754,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkrik bokskog</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Hallenborg</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Hallenborg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>119032494</v>
       </c>
       <c r="B3" t="n">
-        <v>94405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,48 +884,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128856466</v>
+        <v>119032492</v>
       </c>
       <c r="B4" t="n">
-        <v>86857</v>
+        <v>56876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>439</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydlig gyllenspindling</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius bergeronii</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Melot) Melot</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörkavad, Sk</t>
+          <t>längsbäcken, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442259</v>
+        <v>442221</v>
       </c>
       <c r="R4" t="n">
-        <v>6186188</v>
+        <v>6186208</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,31 +972,22 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkrik bokskog</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Joel Hallenborg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Norin, Vincent Vitlock, Clara Lerbro, Gabriella Fjordmark Lerne, Ulf Arup, Maria Ahlefelt, Joachim Krumlinde, Gunilla R Burke, Jan  Olsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Joel Hallenborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44585-2023 artfynd.xlsx
+++ b/artfynd/A 44585-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856466</t>
         </is>
       </c>
     </row>
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119032494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119032492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>